--- a/exports/trend_1d/DELHIVERY_full_report.xlsx
+++ b/exports/trend_1d/DELHIVERY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>32.28</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44783</v>
+        <v>44784</v>
       </c>
       <c r="H2" t="n">
-        <v>599.8</v>
+        <v>563.25</v>
       </c>
       <c r="I2" t="n">
         <v>585.0596948937959</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K2" t="n">
-        <v>20.01</v>
+        <v>12.7</v>
       </c>
       <c r="L2" t="n">
         <v>8.69</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>20.16</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44974</v>
+        <v>44977</v>
       </c>
       <c r="H3" t="n">
-        <v>328.2</v>
+        <v>339.8</v>
       </c>
       <c r="I3" t="n">
         <v>335.3792452117748</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K3" t="n">
-        <v>41.73</v>
+        <v>39.67</v>
       </c>
       <c r="L3" t="n">
         <v>8.07</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.11</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45230</v>
+        <v>45231</v>
       </c>
       <c r="H4" t="n">
-        <v>413.35</v>
+        <v>402.6</v>
       </c>
       <c r="I4" t="n">
         <v>404.9702475754634</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K4" t="n">
-        <v>21.65</v>
+        <v>18.48</v>
       </c>
       <c r="L4" t="n">
         <v>7.56</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45293</v>
+        <v>45294</v>
       </c>
       <c r="H5" t="n">
-        <v>388.55</v>
+        <v>397</v>
       </c>
       <c r="I5" t="n">
         <v>393.9861269827556</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K5" t="n">
-        <v>3.49</v>
+        <v>1.39</v>
       </c>
       <c r="L5" t="n">
         <v>4.21</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.15</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H6" t="n">
-        <v>440.5</v>
+        <v>419.4</v>
       </c>
       <c r="I6" t="n">
         <v>422.234472927994</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K6" t="n">
-        <v>10.96</v>
+        <v>5.64</v>
       </c>
       <c r="L6" t="n">
         <v>3.65</v>
@@ -783,7 +854,7 @@
         <v>0.9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.62</v>
+        <v>4.79</v>
       </c>
       <c r="O6" t="n">
         <v>2.17</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>17.7</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45499</v>
+        <v>45502</v>
       </c>
       <c r="H7" t="n">
-        <v>397</v>
+        <v>412.4</v>
       </c>
       <c r="I7" t="n">
         <v>401.4598917465099</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K7" t="n">
-        <v>5.34</v>
+        <v>1.67</v>
       </c>
       <c r="L7" t="n">
         <v>15.64</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H8" t="n">
-        <v>410.95</v>
+        <v>408.15</v>
       </c>
       <c r="I8" t="n">
         <v>409.1403580713546</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.35</v>
+        <v>-1.03</v>
       </c>
       <c r="L8" t="n">
         <v>4.21</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.85</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="H9" t="n">
-        <v>353</v>
+        <v>371.1</v>
       </c>
       <c r="I9" t="n">
         <v>362.5448131696306</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K9" t="n">
-        <v>13.51</v>
+        <v>9.08</v>
       </c>
       <c r="L9" t="n">
         <v>4.69</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>13.71</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H10" t="n">
-        <v>358.6</v>
+        <v>349.6</v>
       </c>
       <c r="I10" t="n">
         <v>350.546668848297</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.37</v>
+        <v>-5.79</v>
       </c>
       <c r="L10" t="n">
-        <v>5.94</v>
+        <v>6.28</v>
       </c>
       <c r="M10" t="n">
         <v>2.81</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>14.26</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H11" t="n">
-        <v>263.05</v>
+        <v>281.05</v>
       </c>
       <c r="I11" t="n">
         <v>271.1018171027903</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K11" t="n">
-        <v>24.76</v>
+        <v>19.61</v>
       </c>
       <c r="L11" t="n">
         <v>4.75</v>
@@ -1068,7 +1199,7 @@
         <v>2.51</v>
       </c>
       <c r="N11" t="n">
-        <v>4.72</v>
+        <v>6.84</v>
       </c>
       <c r="O11" t="n">
         <v>-2.51</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>17.2</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45867</v>
+        <v>45868</v>
       </c>
       <c r="H12" t="n">
-        <v>421.95</v>
+        <v>409.15</v>
       </c>
       <c r="I12" t="n">
         <v>410.8670819601124</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K12" t="n">
-        <v>50.13</v>
+        <v>45.58</v>
       </c>
       <c r="L12" t="n">
         <v>6.71</v>
@@ -1125,7 +1268,7 @@
         <v>2.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="O12" t="n">
         <v>6.84</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.16</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45870</v>
+        <v>45873</v>
       </c>
       <c r="H13" t="n">
-        <v>429.85</v>
+        <v>461.6</v>
       </c>
       <c r="I13" t="n">
         <v>450.7212425259703</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.06</v>
+        <v>-12.82</v>
       </c>
       <c r="L13" t="n">
-        <v>6.99</v>
+        <v>13.39</v>
       </c>
       <c r="M13" t="n">
-        <v>0.41</v>
+        <v>2.36</v>
       </c>
       <c r="N13" t="n">
-        <v>3.93</v>
+        <v>7.39</v>
       </c>
       <c r="O13" t="n">
         <v>-3.03</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.2</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H14" t="n">
-        <v>455.4</v>
+        <v>445.7</v>
       </c>
       <c r="I14" t="n">
         <v>453.0792982769975</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.34</v>
+        <v>-3.44</v>
       </c>
       <c r="L14" t="n">
         <v>4.68</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>8.56</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="H15" t="n">
-        <v>464.85</v>
+        <v>473.8</v>
       </c>
       <c r="I15" t="n">
         <v>469.9535966248539</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.3</v>
+        <v>-6.3</v>
       </c>
       <c r="L15" t="n">
-        <v>6.69</v>
+        <v>6.93</v>
       </c>
       <c r="M15" t="n">
         <v>0.85</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H16" t="n">
-        <v>484.85</v>
+        <v>442.6</v>
       </c>
       <c r="I16" t="n">
         <v>446.1574037401018</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>2.33</v>
+        <v>-6.59</v>
       </c>
       <c r="L16" t="n">
-        <v>5.88</v>
+        <v>7.89</v>
       </c>
       <c r="M16" t="n">
-        <v>0.47</v>
+        <v>3.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.03</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>1.93</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>13.75</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="H17" t="n">
-        <v>411.8</v>
+        <v>422.95</v>
       </c>
       <c r="I17" t="n">
         <v>414.6803307173255</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K17" t="n">
-        <v>6.96</v>
+        <v>4.44</v>
       </c>
       <c r="L17" t="n">
         <v>6.19</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.7</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="H18" t="n">
-        <v>417.95</v>
+        <v>408.2</v>
       </c>
       <c r="I18" t="n">
         <v>409.2617190646765</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.18</v>
+        <v>-3.49</v>
       </c>
       <c r="L18" t="n">
         <v>5.1</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>10.36</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="H19" t="n">
-        <v>435.9</v>
+        <v>442</v>
       </c>
       <c r="I19" t="n">
         <v>439.7467911434725</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.79</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>8.039999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="M19" t="n">
         <v>2.47</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.32</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H20" t="n">
-        <v>452.35</v>
+        <v>437.25</v>
       </c>
       <c r="I20" t="n">
         <v>438.6815055881501</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K20" t="n">
-        <v>2.34</v>
+        <v>-1.07</v>
       </c>
       <c r="L20" t="n">
         <v>2.67</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>11.16</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="H21" t="n">
-        <v>461.1</v>
+        <v>483.8</v>
       </c>
       <c r="I21" t="n">
         <v>468.0755246903629</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.45</v>
+        <v>-10.65</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>12.45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="N21" t="n">
-        <v>2.96</v>
+        <v>4.92</v>
       </c>
       <c r="O21" t="n">
         <v>-3.34</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.08</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="H22" t="n">
-        <v>484.75</v>
+        <v>467.6</v>
       </c>
       <c r="I22" t="n">
         <v>471.8630721266799</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2</v>
+        <v>-3.35</v>
       </c>
       <c r="L22" t="n">
         <v>4.95</v>
@@ -1695,7 +1958,7 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="O22" t="n">
         <v>4.92</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1755,6 +2030,14 @@
       <c r="Q23" t="n">
         <v>68</v>
       </c>
+      <c r="R23" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3925,7 +4208,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.5</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="6">
@@ -3935,7 +4218,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -3945,7 +4228,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8">
@@ -3955,7 +4238,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -3965,7 +4248,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -3975,7 +4258,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -4015,7 +4298,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.359999999999999</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="15">
@@ -4025,7 +4308,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.220000000000001</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="16">
@@ -4035,7 +4318,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.42</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="17">
@@ -4045,7 +4328,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50.13</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="18">
@@ -4055,7 +4338,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="19">
@@ -4065,7 +4348,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.25</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="20">
@@ -4075,7 +4358,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.94</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="21">
@@ -4105,7 +4388,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4115,7 +4398,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="25">
@@ -4135,7 +4418,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.43</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="27">
@@ -4155,7 +4438,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
